--- a/data/raw/sales/Week 15/Tonor/other_channels.xlsx
+++ b/data/raw/sales/Week 15/Tonor/other_channels.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\sales\Week 15\Tonor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89BEE294-ED40-4182-B7EE-6CBCB23C9C57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81F16AE4-DDB2-42BF-AD3B-B7AC498B2411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -524,7 +524,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
-  <dimension ref="A1:AB956"/>
+  <dimension ref="A1:AA956"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="13.88671875" customWidth="1"/>
@@ -532,10 +532,10 @@
     <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="14.109375" customWidth="1"/>
     <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="28" width="8.6640625" customWidth="1"/>
+    <col min="8" max="27" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>5</v>
       </c>
@@ -577,9 +577,8 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
-      <c r="AB1" s="1"/>
-    </row>
-    <row r="2" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -602,7 +601,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -625,7 +624,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -648,7 +647,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -671,7 +670,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -694,7 +693,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -717,7 +716,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -740,7 +739,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -763,7 +762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -786,7 +785,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -809,7 +808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -832,7 +831,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>52</v>
       </c>
@@ -855,7 +854,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>56</v>
       </c>
@@ -878,7 +877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -901,7 +900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:28" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:27" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
